--- a/scratch-tmp/probe.xlsx
+++ b/scratch-tmp/probe.xlsx
@@ -614,7 +614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B152"/>
+  <dimension ref="A1:B91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="B1">
-        <f>AVERAGE(D!A1:A8)</f>
+        <f>_xlfn.NORM.S.DIST(-8,TRUE)</f>
         <v/>
       </c>
     </row>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B2">
-        <f>AVERAGEA(D!E1:E5)</f>
+        <f>_xlfn.NORM.S.DIST(-20,TRUE)</f>
         <v/>
       </c>
     </row>
@@ -646,7 +646,7 @@
         </is>
       </c>
       <c r="B3">
-        <f>AVERAGE(D!E1:E5)</f>
+        <f>_xlfn.NORM.S.INV(0.000000000001)</f>
         <v/>
       </c>
     </row>
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="B4">
-        <f>COUNT(D!E1:E5)</f>
+        <f>_xlfn.NORM.INV(0.5,3,2)</f>
         <v/>
       </c>
     </row>
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="B5">
-        <f>COUNTA(D!E1:E5)</f>
+        <f>ERFC(5)</f>
         <v/>
       </c>
     </row>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="B6">
-        <f>COUNTBLANK(D!E1:E8)</f>
+        <f>ERFC(20)</f>
         <v/>
       </c>
     </row>
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="B7">
-        <f>COUNT(1,)</f>
+        <f>ERF(3)</f>
         <v/>
       </c>
     </row>
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="B8">
-        <f>COUNTA(1,)</f>
+        <f>GAMMALN(0.5)</f>
         <v/>
       </c>
     </row>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="B9">
-        <f>COUNTA("")</f>
+        <f>GAMMALN(170)</f>
         <v/>
       </c>
     </row>
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="B10">
-        <f>COUNT("3")</f>
+        <f>_xlfn.GAMMA(171)</f>
         <v/>
       </c>
     </row>
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="B11">
-        <f>COUNT(TRUE)</f>
+        <f>_xlfn.GAMMA(0.5)</f>
         <v/>
       </c>
     </row>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B12">
-        <f>COUNTA(D!F1:F5)</f>
+        <f>_xlfn.GAMMA(-0.5)</f>
         <v/>
       </c>
     </row>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="B13">
-        <f>MAX(D!A1:A8)</f>
+        <f>_xlfn.GAMMA(6)</f>
         <v/>
       </c>
     </row>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="B14">
-        <f>MIN(D!A1:A8)</f>
+        <f>_xlfn.T.DIST(0,5,TRUE)</f>
         <v/>
       </c>
     </row>
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="B15">
-        <f>MAXA(D!E1:E5)</f>
+        <f>_xlfn.T.DIST(2.5,1,TRUE)</f>
         <v/>
       </c>
     </row>
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="B16">
-        <f>MINA(D!E1:E5)</f>
+        <f>_xlfn.T.DIST(2.5,1000,TRUE)</f>
         <v/>
       </c>
     </row>
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="B17">
-        <f>MEDIAN(D!A1:A8)</f>
+        <f>_xlfn.T.INV(0.999,3)</f>
         <v/>
       </c>
     </row>
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="B18">
-        <f>MEDIAN(D!A1:A7)</f>
+        <f>_xlfn.T.INV(0.001,3)</f>
         <v/>
       </c>
     </row>
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="B19">
-        <f>_xlfn.MODE.SNGL(D!A1:A8)</f>
+        <f>_xlfn.CHISQ.DIST(100,50,TRUE)</f>
         <v/>
       </c>
     </row>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="B20">
-        <f>_xlfn.MODE.SNGL(D!D1:D8)</f>
+        <f>_xlfn.CHISQ.DIST.RT(100,50)</f>
         <v/>
       </c>
     </row>
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="B21">
-        <f>LARGE(D!A1:A8,3)</f>
+        <f>_xlfn.CHISQ.INV(0.999,50)</f>
         <v/>
       </c>
     </row>
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="B22">
-        <f>SMALL(D!A1:A8,3)</f>
+        <f>_xlfn.F.DIST(3,1,1,TRUE)</f>
         <v/>
       </c>
     </row>
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="B23">
-        <f>_xlfn.RANK.EQ(4,D!A1:A8)</f>
+        <f>_xlfn.F.DIST.RT(0.5,20,30)</f>
         <v/>
       </c>
     </row>
@@ -877,7 +877,7 @@
         </is>
       </c>
       <c r="B24">
-        <f>_xlfn.RANK.EQ(4,D!A1:A8,1)</f>
+        <f>_xlfn.F.INV(0.5,20,30)</f>
         <v/>
       </c>
     </row>
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="B25">
-        <f>_xlfn.RANK.AVG(4,D!A1:A8)</f>
+        <f>_xlfn.BETA.DIST(0.5,2,3,TRUE)</f>
         <v/>
       </c>
     </row>
@@ -899,7 +899,7 @@
         </is>
       </c>
       <c r="B26">
-        <f>_xlfn.PERCENTILE.INC(D!A1:A8,0.25)</f>
+        <f>_xlfn.BETA.DIST(0.001,0.5,0.5,TRUE)</f>
         <v/>
       </c>
     </row>
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="B27">
-        <f>_xlfn.PERCENTILE.EXC(D!A1:A8,0.25)</f>
+        <f>_xlfn.BETA.INV(0.5,2,3)</f>
         <v/>
       </c>
     </row>
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="B28">
-        <f>_xlfn.QUARTILE.INC(D!A1:A8,1)</f>
+        <f>_xlfn.GAMMA.DIST(0.5,0.5,1,TRUE)</f>
         <v/>
       </c>
     </row>
@@ -932,7 +932,7 @@
         </is>
       </c>
       <c r="B29">
-        <f>_xlfn.QUARTILE.EXC(D!A1:A8,1)</f>
+        <f>_xlfn.GAMMA.INV(0.5,0.5,1)</f>
         <v/>
       </c>
     </row>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="B30">
-        <f>_xlfn.PERCENTRANK.INC(D!A1:A8,7)</f>
+        <f>_xlfn.POISSON.DIST(100,50,TRUE)</f>
         <v/>
       </c>
     </row>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="B31">
-        <f>_xlfn.PERCENTRANK.EXC(D!A1:A8,7)</f>
+        <f>_xlfn.BINOM.DIST(500,1000,0.5,TRUE)</f>
         <v/>
       </c>
     </row>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="B32">
-        <f>_xlfn.PERCENTRANK.INC(D!A1:A8,6)</f>
+        <f>_xlfn.BINOM.DIST(0,10,0.001,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="B33">
-        <f>_xlfn.PERCENTRANK.INC(D!A1:A8,3,5)</f>
+        <f>_xlfn.NEGBINOM.DIST(0,1,0.5,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="B34">
-        <f>_xlfn.STDEV.S(D!A1:A8)</f>
+        <f>_xlfn.HYPGEOM.DIST(2,5,10,50,TRUE)</f>
         <v/>
       </c>
     </row>
@@ -998,7 +998,7 @@
         </is>
       </c>
       <c r="B35">
-        <f>_xlfn.STDEV.P(D!A1:A8)</f>
+        <f>_xlfn.WEIBULL.DIST(0,2,1,TRUE)</f>
         <v/>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="B36">
-        <f>STDEVA(D!E1:E5)</f>
+        <f>_xlfn.EXPON.DIST(0,3,TRUE)</f>
         <v/>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="B37">
-        <f>STDEVPA(D!E1:E5)</f>
+        <f>_xlfn.LOGNORM.DIST(1,0,1,TRUE)</f>
         <v/>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="B38">
-        <f>_xlfn.VAR.S(D!A1:A8)</f>
+        <f>_xlfn.CONFIDENCE.T(0.01,2.5,10)</f>
         <v/>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="B39">
-        <f>_xlfn.VAR.P(D!A1:A8)</f>
+        <f>_xlfn.Z.TEST(D!B1:B8,8)</f>
         <v/>
       </c>
     </row>
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="B40">
-        <f>VARA(D!E1:E5)</f>
+        <f>FISHER(-0.5)</f>
         <v/>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="B41">
-        <f>VARPA(D!E1:E5)</f>
+        <f>STANDARDIZE(1,0,1)</f>
         <v/>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="B42">
-        <f>DEVSQ(D!A1:A8)</f>
+        <f>SUM(LINEST(D!G1:G5,D!H1:H5))</f>
         <v/>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
         </is>
       </c>
       <c r="B43">
-        <f>AVEDEV(D!A1:A8)</f>
+        <f>INDEX(LINEST(D!G1:G5,D!H1:H8,FALSE),1,1)</f>
         <v/>
       </c>
     </row>
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="B44">
-        <f>GEOMEAN(D!A1:A8)</f>
+        <f>INDEX(TREND(D!G1:G5,D!H1:H5,{6;7}),1,1)</f>
         <v/>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c r="B45">
-        <f>HARMEAN(D!A1:A8)</f>
+        <f>INDEX(TREND(D!G1:G5,D!H1:H5,{6;7}),2,1)</f>
         <v/>
       </c>
     </row>
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="B46">
-        <f>TRIMMEAN(D!A1:A8,0.25)</f>
+        <f>INDEX(TREND(D!G1:G5),3,1)</f>
         <v/>
       </c>
     </row>
@@ -1130,7 +1130,7 @@
         </is>
       </c>
       <c r="B47">
-        <f>STANDARDIZE(7,5,2)</f>
+        <f>INDEX(GROWTH(D!G1:G5,D!H1:H5,{6}),1,1)</f>
         <v/>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
         </is>
       </c>
       <c r="B48">
-        <f>SKEW(D!A1:A8)</f>
+        <f>INDEX(LINEST(D!G1:G5,D!H1:I5),1,1)</f>
         <v/>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
         </is>
       </c>
       <c r="B49">
-        <f>_xlfn.SKEW.P(D!A1:A8)</f>
+        <f>INDEX(LINEST(D!G1:G5,D!H1:I5),1,2)</f>
         <v/>
       </c>
     </row>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="B50">
-        <f>KURT(D!A1:A8)</f>
+        <f>INDEX(LINEST(D!G1:G5,D!H1:I5),1,3)</f>
         <v/>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
         </is>
       </c>
       <c r="B51">
-        <f>COUNTIF(D!C1:C4,"a")</f>
+        <f>INDEX(TREND(D!G1:G5,D!H1:I5,D!H1:I5),2,1)</f>
         <v/>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
         </is>
       </c>
       <c r="B52">
-        <f>COUNTIFS(D!C1:C4,"a",D!A1:A4,"&gt;4")</f>
+        <f>COUNTIF(D!A1:A8,"&gt;=5")</f>
         <v/>
       </c>
     </row>
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="B53">
-        <f>AVERAGEIF(D!A1:A8,"&gt;4")</f>
+        <f>COUNTIF(D!C1:C4,"&lt;&gt;a")</f>
         <v/>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="B54">
-        <f>AVERAGEIF(D!C1:C4,"a",D!A1:A4)</f>
+        <f>COUNTIF(D!C1:C4,"a*")</f>
         <v/>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="B55">
-        <f>AVERAGEIFS(D!A1:A8,D!A1:A8,"&gt;4")</f>
+        <f>COUNTIF(D!E1:E5,"")</f>
         <v/>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B56">
-        <f>_xlfn.MAXIFS(D!A1:A8,D!B1:B8,"&gt;6")</f>
+        <f>COUNTBLANK(D!C1:C8)</f>
         <v/>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="B57">
-        <f>_xlfn.MINIFS(D!A1:A8,D!B1:B8,"&gt;6")</f>
+        <f>AVERAGEIF(D!A1:A8,"&gt;100")</f>
         <v/>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="B58">
-        <f>_xlfn.COVARIANCE.P(D!G1:G5,D!H1:H5)</f>
+        <f>_xlfn.MAXIFS(D!A1:A8,D!A1:A8,"&gt;100")</f>
         <v/>
       </c>
     </row>
@@ -1262,7 +1262,7 @@
         </is>
       </c>
       <c r="B59">
-        <f>_xlfn.COVARIANCE.S(D!G1:G5,D!H1:H5)</f>
+        <f>_xlfn.MINIFS(D!A1:A8,D!A1:A8,"&gt;100")</f>
         <v/>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="B60">
-        <f>CORREL(D!G1:G5,D!H1:H5)</f>
+        <f>SMALL(D!A1:A8,1)</f>
         <v/>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="B61">
-        <f>PEARSON(D!G1:G5,D!H1:H5)</f>
+        <f>LARGE(D!A1:A8,8)</f>
         <v/>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="B62">
-        <f>RSQ(D!G1:G5,D!H1:H5)</f>
+        <f>MEDIAN(1,2,3,4)</f>
         <v/>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
         </is>
       </c>
       <c r="B63">
-        <f>SLOPE(D!G1:G5,D!H1:H5)</f>
+        <f>_xlfn.MODE.MULT(1,2,2,3,3)</f>
         <v/>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
         </is>
       </c>
       <c r="B64">
-        <f>INTERCEPT(D!G1:G5,D!H1:H5)</f>
+        <f>_xlfn.QUARTILE.INC(D!A1:A8,0)</f>
         <v/>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
         </is>
       </c>
       <c r="B65">
-        <f>_xlfn.FORECAST.LINEAR(6,D!G1:G5,D!H1:H5)</f>
+        <f>_xlfn.QUARTILE.INC(D!A1:A8,4)</f>
         <v/>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="B66">
-        <f>SUM(TREND(D!G1:G5,D!H1:H5,D!H1:H5))</f>
+        <f>_xlfn.PERCENTILE.INC(D!A1:A8,0)</f>
         <v/>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
         </is>
       </c>
       <c r="B67">
-        <f>SUM(GROWTH(D!G1:G5,D!H1:H5,D!H1:H5))</f>
+        <f>_xlfn.PERCENTILE.INC(D!A1:A8,1)</f>
         <v/>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="B68">
-        <f>INDEX(LINEST(D!G1:G5,D!H1:H5),1,1)</f>
+        <f>_xlfn.PERCENTRANK.INC(D!A1:A8,3)</f>
         <v/>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
         </is>
       </c>
       <c r="B69">
-        <f>INDEX(LINEST(D!G1:G5,D!H1:H5),1,2)</f>
+        <f>_xlfn.PERCENTRANK.INC(D!A1:A8,11)</f>
         <v/>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="B70">
-        <f>INDEX(LINEST(D!G1:G5,D!H1:H5,TRUE,TRUE),2,1)</f>
+        <f>SKEW(1,2,3,4,5)</f>
         <v/>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B71">
-        <f>INDEX(LINEST(D!G1:G5,D!H1:H5,TRUE,TRUE),3,1)</f>
+        <f>KURT(1,2,3,4,5)</f>
         <v/>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="B72">
-        <f>INDEX(LINEST(D!G1:G5,D!H1:H5,TRUE,TRUE),3,2)</f>
+        <f>GEOMEAN(1,2,3,4)</f>
         <v/>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
         </is>
       </c>
       <c r="B73">
-        <f>INDEX(LINEST(D!G1:G5,D!H1:H5,TRUE,TRUE),4,1)</f>
+        <f>HARMEAN(1,2,3,4)</f>
         <v/>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="B74">
-        <f>INDEX(LINEST(D!G1:G5,D!H1:H5,TRUE,TRUE),4,2)</f>
+        <f>TRIMMEAN({1,2,3,4,5,6,7,8,9,10},0.2)</f>
         <v/>
       </c>
     </row>
@@ -1438,7 +1438,7 @@
         </is>
       </c>
       <c r="B75">
-        <f>INDEX(LINEST(D!G1:G5,D!H1:H5,TRUE,TRUE),5,1)</f>
+        <f>AVEDEV(1,2,3,4)</f>
         <v/>
       </c>
     </row>
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="B76">
-        <f>INDEX(LINEST(D!G1:G5,D!H1:H5,TRUE,TRUE),5,2)</f>
+        <f>DEVSQ(1,2,3,4)</f>
         <v/>
       </c>
     </row>
@@ -1460,7 +1460,7 @@
         </is>
       </c>
       <c r="B77">
-        <f>INDEX(FREQUENCY(D!A1:A8,{4,8}),1,1)</f>
+        <f>_xlfn.VAR.S(1,2)</f>
         <v/>
       </c>
     </row>
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="B78">
-        <f>INDEX(FREQUENCY(D!A1:A8,{4,8}),2,1)</f>
+        <f>_xlfn.VAR.P(1)</f>
         <v/>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
         </is>
       </c>
       <c r="B79">
-        <f>INDEX(FREQUENCY(D!A1:A8,{4,8}),3,1)</f>
+        <f>_xlfn.STDEV.S(1,2,3)</f>
         <v/>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="B80">
-        <f>PROB({1,2,3,4},{0.1,0.2,0.3,0.4},2,3)</f>
+        <f>_xlfn.COVARIANCE.P({1,2,3},{4,5,7})</f>
         <v/>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
         </is>
       </c>
       <c r="B81">
-        <f>PROB({1,2,3,4},{0.1,0.2,0.3,0.4},2)</f>
+        <f>CORREL({1,2,3},{4,5,7})</f>
         <v/>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B82">
-        <f>_xlfn.NORM.DIST(1.5,0,1,TRUE)</f>
+        <f>RSQ({1,2,3},{4,5,7})</f>
         <v/>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="B83">
-        <f>_xlfn.NORM.DIST(1.5,0,1,FALSE)</f>
+        <f>SLOPE({1,2,3},{4,5,7})</f>
         <v/>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
         </is>
       </c>
       <c r="B84">
-        <f>_xlfn.NORM.DIST(42,40,1.5,TRUE)</f>
+        <f>INTERCEPT({1,2,3},{4,5,7})</f>
         <v/>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="B85">
-        <f>_xlfn.NORM.INV(0.908789,40,1.5)</f>
+        <f>_xlfn.FORECAST.LINEAR(4,{1,2,3},{4,5,7})</f>
         <v/>
       </c>
     </row>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="B86">
-        <f>_xlfn.NORM.S.DIST(1.333333,TRUE)</f>
+        <f>PROB({0,1,2,3},{0.2,0.3,0.1,0.4},1,3)</f>
         <v/>
       </c>
     </row>
@@ -1570,7 +1570,7 @@
         </is>
       </c>
       <c r="B87">
-        <f>_xlfn.NORM.S.DIST(-3,TRUE)</f>
+        <f>INDEX(FREQUENCY({1,2,3,4,5,6},{2,4}),2,1)</f>
         <v/>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
         </is>
       </c>
       <c r="B88">
-        <f>_xlfn.NORM.S.DIST(1.333333,FALSE)</f>
+        <f>_xlfn.T.TEST(D!A1:A8,D!B1:B8,2,2)</f>
         <v/>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="B89">
-        <f>_xlfn.NORM.S.INV(0.908789)</f>
+        <f>_xlfn.T.TEST(D!A1:A8,D!B1:B8,2,3)</f>
         <v/>
       </c>
     </row>
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="B90">
-        <f>_xlfn.NORM.S.INV(0.0000001)</f>
+        <f>_xlfn.F.TEST(D!A1:A8,D!B1:B8)</f>
         <v/>
       </c>
     </row>
@@ -1614,678 +1614,7 @@
         </is>
       </c>
       <c r="B91">
-        <f>_xlfn.LOGNORM.DIST(4,3.5,1.2,TRUE)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>case92</t>
-        </is>
-      </c>
-      <c r="B92">
-        <f>_xlfn.LOGNORM.DIST(4,3.5,1.2,FALSE)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>case93</t>
-        </is>
-      </c>
-      <c r="B93">
-        <f>_xlfn.LOGNORM.INV(0.039084,3.5,1.2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>case94</t>
-        </is>
-      </c>
-      <c r="B94">
-        <f>_xlfn.PHI(0.75)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>case95</t>
-        </is>
-      </c>
-      <c r="B95">
-        <f>_xlfn.GAUSS(2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>case96</t>
-        </is>
-      </c>
-      <c r="B96">
-        <f>_xlfn.CONFIDENCE.NORM(0.05,2.5,50)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>case97</t>
-        </is>
-      </c>
-      <c r="B97">
-        <f>_xlfn.CONFIDENCE.T(0.05,1,50)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>case98</t>
-        </is>
-      </c>
-      <c r="B98">
-        <f>_xlfn.T.DIST(60,1,TRUE)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>case99</t>
-        </is>
-      </c>
-      <c r="B99">
-        <f>_xlfn.T.DIST(-1.5,10,TRUE)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>case100</t>
-        </is>
-      </c>
-      <c r="B100">
-        <f>_xlfn.T.DIST(1.5,10,FALSE)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>case101</t>
-        </is>
-      </c>
-      <c r="B101">
-        <f>_xlfn.T.DIST.2T(1.96,60)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>case102</t>
-        </is>
-      </c>
-      <c r="B102">
-        <f>_xlfn.T.DIST.RT(1.96,60)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>case103</t>
-        </is>
-      </c>
-      <c r="B103">
-        <f>_xlfn.T.INV(0.75,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>case104</t>
-        </is>
-      </c>
-      <c r="B104">
-        <f>_xlfn.T.INV(0.05,10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>case105</t>
-        </is>
-      </c>
-      <c r="B105">
-        <f>_xlfn.T.INV.2T(0.05,10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>case106</t>
-        </is>
-      </c>
-      <c r="B106">
-        <f>_xlfn.F.DIST(15.2069,6,4,TRUE)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>case107</t>
-        </is>
-      </c>
-      <c r="B107">
-        <f>_xlfn.F.DIST(15.2069,6,4,FALSE)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>case108</t>
-        </is>
-      </c>
-      <c r="B108">
-        <f>_xlfn.F.DIST.RT(15.2069,6,4)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>case109</t>
-        </is>
-      </c>
-      <c r="B109">
-        <f>_xlfn.F.INV(0.01,6,4)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>case110</t>
-        </is>
-      </c>
-      <c r="B110">
-        <f>_xlfn.F.INV.RT(0.01,6,4)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>case111</t>
-        </is>
-      </c>
-      <c r="B111">
-        <f>_xlfn.CHISQ.DIST(0.5,1,TRUE)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>case112</t>
-        </is>
-      </c>
-      <c r="B112">
-        <f>_xlfn.CHISQ.DIST(0.5,1,FALSE)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>case113</t>
-        </is>
-      </c>
-      <c r="B113">
-        <f>_xlfn.CHISQ.DIST.RT(18.307,10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>case114</t>
-        </is>
-      </c>
-      <c r="B114">
-        <f>_xlfn.CHISQ.INV(0.93,1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>case115</t>
-        </is>
-      </c>
-      <c r="B115">
-        <f>_xlfn.CHISQ.INV.RT(0.05,10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>case116</t>
-        </is>
-      </c>
-      <c r="B116">
-        <f>_xlfn.BINOM.DIST(6,10,0.5,FALSE)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>case117</t>
-        </is>
-      </c>
-      <c r="B117">
-        <f>_xlfn.BINOM.DIST(6,10,0.5,TRUE)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>case118</t>
-        </is>
-      </c>
-      <c r="B118">
-        <f>_xlfn.BINOM.DIST(60,100,0.5,TRUE)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>case119</t>
-        </is>
-      </c>
-      <c r="B119">
-        <f>_xlfn.BINOM.INV(6,0.5,0.75)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>case120</t>
-        </is>
-      </c>
-      <c r="B120">
-        <f>_xlfn.BINOM.INV(100,0.3,0.95)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>case121</t>
-        </is>
-      </c>
-      <c r="B121">
-        <f>_xlfn.NEGBINOM.DIST(10,5,0.25,FALSE)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>case122</t>
-        </is>
-      </c>
-      <c r="B122">
-        <f>_xlfn.NEGBINOM.DIST(10,5,0.25,TRUE)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>case123</t>
-        </is>
-      </c>
-      <c r="B123">
-        <f>_xlfn.POISSON.DIST(2,5,FALSE)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>case124</t>
-        </is>
-      </c>
-      <c r="B124">
-        <f>_xlfn.POISSON.DIST(2,5,TRUE)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>case125</t>
-        </is>
-      </c>
-      <c r="B125">
-        <f>_xlfn.HYPGEOM.DIST(1,4,8,20,FALSE)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>case126</t>
-        </is>
-      </c>
-      <c r="B126">
-        <f>_xlfn.HYPGEOM.DIST(1,4,8,20,TRUE)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>case127</t>
-        </is>
-      </c>
-      <c r="B127">
-        <f>_xlfn.EXPON.DIST(0.2,10,TRUE)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>case128</t>
-        </is>
-      </c>
-      <c r="B128">
-        <f>_xlfn.EXPON.DIST(0.2,10,FALSE)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>case129</t>
-        </is>
-      </c>
-      <c r="B129">
-        <f>_xlfn.WEIBULL.DIST(105,20,100,TRUE)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>case130</t>
-        </is>
-      </c>
-      <c r="B130">
-        <f>_xlfn.WEIBULL.DIST(105,20,100,FALSE)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>case131</t>
-        </is>
-      </c>
-      <c r="B131">
-        <f>_xlfn.GAMMA.DIST(10,9,2,TRUE)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>case132</t>
-        </is>
-      </c>
-      <c r="B132">
-        <f>_xlfn.GAMMA.DIST(10,9,2,FALSE)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>case133</t>
-        </is>
-      </c>
-      <c r="B133">
-        <f>_xlfn.GAMMA.INV(0.068094,9,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>case134</t>
-        </is>
-      </c>
-      <c r="B134">
-        <f>_xlfn.BETA.DIST(2,8,10,TRUE,1,3)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>case135</t>
-        </is>
-      </c>
-      <c r="B135">
-        <f>_xlfn.BETA.DIST(2,8,10,FALSE,1,3)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>case136</t>
-        </is>
-      </c>
-      <c r="B136">
-        <f>_xlfn.BETA.INV(0.6854706,8,10,1,3)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>case137</t>
-        </is>
-      </c>
-      <c r="B137">
-        <f>_xlfn.GAMMA(2.5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>case138</t>
-        </is>
-      </c>
-      <c r="B138">
-        <f>_xlfn.GAMMA(-3.75)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>case139</t>
-        </is>
-      </c>
-      <c r="B139">
-        <f>GAMMALN(4.5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>case140</t>
-        </is>
-      </c>
-      <c r="B140">
-        <f>FISHER(0.75)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>case141</t>
-        </is>
-      </c>
-      <c r="B141">
-        <f>FISHERINV(0.972955)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>case142</t>
-        </is>
-      </c>
-      <c r="B142">
-        <f>ERF(0.745)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>case143</t>
-        </is>
-      </c>
-      <c r="B143">
-        <f>ERF(1,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>case144</t>
-        </is>
-      </c>
-      <c r="B144">
-        <f>ERFC(1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>case145</t>
-        </is>
-      </c>
-      <c r="B145">
-        <f>ERFC(-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>case146</t>
-        </is>
-      </c>
-      <c r="B146">
-        <f>_xlfn.Z.TEST(D!A1:A8,4)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>case147</t>
-        </is>
-      </c>
-      <c r="B147">
-        <f>_xlfn.Z.TEST(D!A1:A8,4,1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>case148</t>
-        </is>
-      </c>
-      <c r="B148">
-        <f>_xlfn.T.TEST(D!A1:A5,D!G1:G5,2,1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>case149</t>
-        </is>
-      </c>
-      <c r="B149">
-        <f>_xlfn.T.TEST(D!A1:A5,D!G1:G5,1,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>case150</t>
-        </is>
-      </c>
-      <c r="B150">
-        <f>_xlfn.T.TEST(D!A1:A5,D!G1:G5,2,3)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>case151</t>
-        </is>
-      </c>
-      <c r="B151">
-        <f>_xlfn.F.TEST(D!A1:A5,D!G1:G5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>case152</t>
-        </is>
-      </c>
-      <c r="B152">
-        <f>_xlfn.CHISQ.TEST({58,35;11,25},{45.35,47.65;17.65,18.35})</f>
+        <f>_xlfn.CHISQ.TEST({10,20,30},{15,20,25})</f>
         <v/>
       </c>
     </row>
